--- a/slcsos26/xlsfiles/PROCESSED-VARS.xlsx
+++ b/slcsos26/xlsfiles/PROCESSED-VARS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rodi\Github\kingair-Sys26-work\slcsos26\xlsfiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfre\Github\kingair-Sys26-work\slcsos26\xlsfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E2C178-D6C6-4599-93FF-5D92071E76F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF673DF-0208-4236-B277-E9EDE463A745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-465" yWindow="795" windowWidth="28800" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="17280" windowHeight="9912" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="defines2" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="227">
   <si>
     <t>LICOR7000</t>
   </si>
@@ -337,9 +337,6 @@
     <t>TIME14D</t>
   </si>
   <si>
-    <t>ps_CPT6140</t>
-  </si>
-  <si>
     <t>TEMPX</t>
   </si>
   <si>
@@ -697,16 +694,13 @@
     <t>BuckBoardTemp</t>
   </si>
   <si>
-    <t>BuckMirrorFlag</t>
-  </si>
-  <si>
-    <t>BuckDataFlag</t>
-  </si>
-  <si>
     <t>TransducerOvenRTD</t>
   </si>
   <si>
     <t>WaterBlockRTD</t>
+  </si>
+  <si>
+    <t>tdpFlag</t>
   </si>
 </sst>
 </file>
@@ -1597,15 +1591,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B228E37-496C-47C1-AF6B-8A30EDF5FB04}">
-  <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="18" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="18" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>103</v>
       </c>
@@ -1613,7 +1607,7 @@
         <v>55</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>57</v>
@@ -1622,13 +1616,13 @@
         <v>58</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="I1" s="8" t="s">
         <v>2</v>
@@ -1640,13 +1634,13 @@
         <v>27</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O1" s="8" t="s">
         <v>1</v>
@@ -1655,15 +1649,15 @@
         <v>3</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -1675,7 +1669,7 @@
         <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F2" t="s">
         <v>39</v>
@@ -1687,7 +1681,7 @@
         <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
         <v>30</v>
@@ -1696,13 +1690,13 @@
         <v>29</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O2" t="s">
         <v>36</v>
@@ -1717,7 +1711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -1725,13 +1719,13 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
         <v>40</v>
@@ -1743,16 +1737,16 @@
         <v>97</v>
       </c>
       <c r="I3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P3" s="4" t="s">
         <v>38</v>
@@ -1764,7 +1758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -1775,7 +1769,7 @@
         <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
@@ -1787,19 +1781,19 @@
         <v>98</v>
       </c>
       <c r="I4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J4" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>17</v>
@@ -1808,7 +1802,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1819,7 +1813,7 @@
         <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F5" t="s">
         <v>42</v>
@@ -1831,19 +1825,19 @@
         <v>99</v>
       </c>
       <c r="I5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J5" t="s">
         <v>33</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>21</v>
@@ -1852,18 +1846,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -1875,36 +1869,36 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -1916,33 +1910,33 @@
         <v>101</v>
       </c>
       <c r="I7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F8" t="s">
         <v>45</v>
@@ -1954,22 +1948,22 @@
         <v>102</v>
       </c>
       <c r="I8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>24</v>
       </c>
@@ -1977,35 +1971,35 @@
         <v>66</v>
       </c>
       <c r="E9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>23</v>
       </c>
@@ -2013,66 +2007,66 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F10" t="s">
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
         <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" t="s">
         <v>135</v>
       </c>
-      <c r="H11" t="s">
-        <v>136</v>
-      </c>
       <c r="I11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>49</v>
       </c>
@@ -2080,28 +2074,28 @@
         <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>50</v>
       </c>
@@ -2109,19 +2103,19 @@
         <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -2129,28 +2123,28 @@
         <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D15" t="s">
         <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>34</v>
       </c>
@@ -2158,14 +2152,14 @@
         <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P16" s="5"/>
       <c r="Q16" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>35</v>
       </c>
@@ -2173,133 +2167,133 @@
         <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P17" s="5"/>
       <c r="Q17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" t="s">
         <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="Q18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
         <v>83</v>
       </c>
       <c r="E19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
         <v>84</v>
       </c>
       <c r="E20" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P20" s="5"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D21" t="s">
         <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P21" s="5"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D22" t="s">
         <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="2"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D23" t="s">
         <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q23" s="2"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" t="s">
         <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P24" s="5"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
         <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D27" t="s">
         <v>91</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>190</v>
       </c>
@@ -2307,16 +2301,16 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D29" t="s">
         <v>93</v>
       </c>
       <c r="P29" s="5"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>217</v>
       </c>
@@ -2324,99 +2318,89 @@
         <v>94</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D31" t="s">
         <v>95</v>
       </c>
       <c r="P31" s="5"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>215</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P32" s="5"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="D33" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>188</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="D35" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
+    <row r="37" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
         <v>219</v>
       </c>
-      <c r="D36" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B38" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B39" s="9" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B41" s="9" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B42" s="9" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="9" t="s">
+    <row r="43" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B43" s="9" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="9" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="9" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="9" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
